--- a/PosAllCompoundSearch.xlsx
+++ b/PosAllCompoundSearch.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/dreece23_uw_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\dreece23\pca-sims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{2520C651-78D0-4DFE-A568-9076C7AEFACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{167AF0B2-17BB-42DF-82B6-71088F53CF01}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1ABCFFB-074C-4317-BFDE-658F7D19FEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F0003782-33DB-42AD-8C46-AD7EE89F812D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F0003782-33DB-42AD-8C46-AD7EE89F812D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="146">
   <si>
     <t>Area Norm. By Total Ion Intensity Statistics</t>
   </si>
@@ -471,6 +471,9 @@
   <si>
     <t>P3_SQ0</t>
   </si>
+  <si>
+    <t>Fragment</t>
+  </si>
 </sst>
 </file>
 
@@ -568,10 +571,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -872,17 +871,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACD0E45-4787-45F3-91D8-F3E911E60EEC}">
   <dimension ref="A1:T127"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>145</v>
+      </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -941,7 +943,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1003,7 +1005,7 @@
         <v>2.33E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1065,7 +1067,7 @@
         <v>3.1399999999999999E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1127,7 +1129,7 @@
         <v>6.3400000000000001E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1189,7 +1191,7 @@
         <v>1.74E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1251,7 +1253,7 @@
         <v>2.1800000000000001E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1313,7 +1315,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1375,7 +1377,7 @@
         <v>6.9800000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1437,7 +1439,7 @@
         <v>1.14E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1499,7 +1501,7 @@
         <v>2.7699999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1561,7 +1563,7 @@
         <v>1.4E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1623,7 +1625,7 @@
         <v>9.4600000000000001E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1685,7 +1687,7 @@
         <v>1.48E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1747,7 +1749,7 @@
         <v>2.3E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1809,7 +1811,7 @@
         <v>8.6700000000000006E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1871,7 +1873,7 @@
         <v>1.64E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1933,7 +1935,7 @@
         <v>4.7899999999999999E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1995,7 +1997,7 @@
         <v>1.47E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2057,7 +2059,7 @@
         <v>1.6899999999999998E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2119,7 +2121,7 @@
         <v>5.8699999999999996E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2181,7 +2183,7 @@
         <v>9.8700000000000003E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2243,7 +2245,7 @@
         <v>7.7099999999999998E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2305,7 +2307,7 @@
         <v>7.92E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2367,7 +2369,7 @@
         <v>1.2199999999999999E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2429,7 +2431,7 @@
         <v>2.1699999999999999E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2491,7 +2493,7 @@
         <v>3.46E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2553,7 +2555,7 @@
         <v>1.9E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2615,7 +2617,7 @@
         <v>6.2600000000000004E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2677,7 +2679,7 @@
         <v>2.4499999999999999E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2739,7 +2741,7 @@
         <v>2.7799999999999999E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2801,7 +2803,7 @@
         <v>1.11E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2863,7 +2865,7 @@
         <v>2.6200000000000003E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2925,7 +2927,7 @@
         <v>3.1700000000000001E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -2987,7 +2989,7 @@
         <v>6.7599999999999995E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -3049,7 +3051,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -3111,7 +3113,7 @@
         <v>6.28E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -3173,7 +3175,7 @@
         <v>7.0200000000000004E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -3235,7 +3237,7 @@
         <v>4.3E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -3297,7 +3299,7 @@
         <v>5.3200000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -3359,7 +3361,7 @@
         <v>2.9799999999999998E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -3421,7 +3423,7 @@
         <v>3.4499999999999998E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -3483,7 +3485,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -3545,7 +3547,7 @@
         <v>2.5799999999999998E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -3607,7 +3609,7 @@
         <v>2.34E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -3669,7 +3671,7 @@
         <v>6.5300000000000004E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -3731,7 +3733,7 @@
         <v>1.1800000000000001E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -3793,7 +3795,7 @@
         <v>2.0799999999999999E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -3855,7 +3857,7 @@
         <v>4.4600000000000004E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -3917,7 +3919,7 @@
         <v>1.0300000000000001E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -3979,7 +3981,7 @@
         <v>4.9500000000000004E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -4041,7 +4043,7 @@
         <v>1.06E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -4103,7 +4105,7 @@
         <v>4.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -4165,7 +4167,7 @@
         <v>3.6600000000000001E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -4227,7 +4229,7 @@
         <v>7.3300000000000004E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -4289,7 +4291,7 @@
         <v>6.1899999999999998E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -4351,7 +4353,7 @@
         <v>1.16E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -4413,7 +4415,7 @@
         <v>5.9900000000000003E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -4475,7 +4477,7 @@
         <v>1.8100000000000001E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -4537,7 +4539,7 @@
         <v>2.0300000000000001E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -4599,7 +4601,7 @@
         <v>9.5600000000000004E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -4661,7 +4663,7 @@
         <v>8.8199999999999997E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -4723,7 +4725,7 @@
         <v>6.5499999999999998E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -4785,7 +4787,7 @@
         <v>1.27E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -4847,7 +4849,7 @@
         <v>1.4300000000000001E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -4909,7 +4911,7 @@
         <v>4.95E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -4971,7 +4973,7 @@
         <v>4.6000000000000001E-4</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -5033,7 +5035,7 @@
         <v>4.6000000000000001E-4</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -5095,7 +5097,7 @@
         <v>2.8200000000000002E-4</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -5157,7 +5159,7 @@
         <v>2.6200000000000003E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -5219,7 +5221,7 @@
         <v>1.2700000000000001E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -5281,7 +5283,7 @@
         <v>1.32E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -5343,7 +5345,7 @@
         <v>5.7299999999999999E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -5405,7 +5407,7 @@
         <v>2.98E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -5467,7 +5469,7 @@
         <v>5.8900000000000003E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -5529,7 +5531,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -5591,7 +5593,7 @@
         <v>8.9499999999999996E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -5653,7 +5655,7 @@
         <v>2.6200000000000003E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -5715,7 +5717,7 @@
         <v>5.6400000000000005E-4</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -5777,7 +5779,7 @@
         <v>2.1199999999999999E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -5839,7 +5841,7 @@
         <v>2.7300000000000002E-4</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -5901,7 +5903,7 @@
         <v>7.4700000000000005E-4</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -5963,7 +5965,7 @@
         <v>4.3399999999999998E-4</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -6025,7 +6027,7 @@
         <v>3.79E-4</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -6087,7 +6089,7 @@
         <v>1.27E-4</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -6149,7 +6151,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -6211,7 +6213,7 @@
         <v>8.4699999999999999E-4</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -6273,7 +6275,7 @@
         <v>5.5599999999999996E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -6335,7 +6337,7 @@
         <v>2.0599999999999999E-4</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -6397,7 +6399,7 @@
         <v>3.68E-4</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -6459,7 +6461,7 @@
         <v>3.68E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -6521,7 +6523,7 @@
         <v>2.3599999999999999E-4</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -6583,7 +6585,7 @@
         <v>6.1799999999999995E-4</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -6645,7 +6647,7 @@
         <v>5.9199999999999997E-4</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -6707,7 +6709,7 @@
         <v>3.5300000000000002E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -6769,7 +6771,7 @@
         <v>2.99E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -6831,7 +6833,7 @@
         <v>2.99E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -6893,7 +6895,7 @@
         <v>1.31E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -6955,7 +6957,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -7017,7 +7019,7 @@
         <v>3.1799999999999998E-4</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -7079,7 +7081,7 @@
         <v>4.6299999999999998E-4</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -7141,7 +7143,7 @@
         <v>5.9900000000000003E-4</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -7203,7 +7205,7 @@
         <v>5.9900000000000003E-4</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -7265,7 +7267,7 @@
         <v>1.91E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -7327,7 +7329,7 @@
         <v>1.67E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -7389,7 +7391,7 @@
         <v>4.9500000000000004E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -7451,7 +7453,7 @@
         <v>3.9300000000000001E-4</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -7513,7 +7515,7 @@
         <v>5.9000000000000003E-4</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -7575,7 +7577,7 @@
         <v>4.0099999999999999E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -7637,7 +7639,7 @@
         <v>4.0099999999999999E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -7699,7 +7701,7 @@
         <v>2.8899999999999998E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -7761,7 +7763,7 @@
         <v>2.72E-4</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -7823,7 +7825,7 @@
         <v>2.0100000000000001E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -7885,7 +7887,7 @@
         <v>2.0100000000000001E-4</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -7947,7 +7949,7 @@
         <v>5.1500000000000005E-4</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -8009,7 +8011,7 @@
         <v>2.9500000000000001E-4</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -8071,7 +8073,7 @@
         <v>3.5300000000000002E-4</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -8133,7 +8135,7 @@
         <v>2.9500000000000001E-4</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -8195,7 +8197,7 @@
         <v>1.4100000000000001E-4</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -8257,7 +8259,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -8319,7 +8321,7 @@
         <v>3.8200000000000002E-4</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -8381,7 +8383,7 @@
         <v>4.2299999999999998E-4</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -8443,7 +8445,7 @@
         <v>4.8799999999999999E-4</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -8505,7 +8507,7 @@
         <v>4.8799999999999999E-4</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -8567,7 +8569,7 @@
         <v>7.6800000000000002E-4</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -8629,7 +8631,7 @@
         <v>7.6800000000000002E-4</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -8699,13 +8701,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C35922-25D4-405A-B403-152CE1DDA46A}">
   <dimension ref="A1:S118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="19" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.73046875" customWidth="1"/>
+    <col min="2" max="19" width="9.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -8764,7 +8766,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
         <v>11.99812</v>
       </c>
@@ -8823,7 +8825,7 @@
         <v>2.33E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="4">
         <v>13.0059</v>
       </c>
@@ -8882,7 +8884,7 @@
         <v>3.1399999999999999E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>14.013999999999999</v>
       </c>
@@ -8941,7 +8943,7 @@
         <v>6.3400000000000001E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="4">
         <v>15.02271</v>
       </c>
@@ -9000,7 +9002,7 @@
         <v>1.74E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>19.017900000000001</v>
       </c>
@@ -9059,7 +9061,7 @@
         <v>2.1800000000000001E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
         <v>26.014060000000001</v>
       </c>
@@ -9118,7 +9120,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>26.980969999999999</v>
       </c>
@@ -9177,7 +9179,7 @@
         <v>6.9800000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
         <v>27.022760000000002</v>
       </c>
@@ -9236,7 +9238,7 @@
         <v>1.14E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>27.98413</v>
       </c>
@@ -9295,7 +9297,7 @@
         <v>2.7699999999999999E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="4">
         <v>27.987130000000001</v>
       </c>
@@ -9354,7 +9356,7 @@
         <v>1.4E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>28.03013</v>
       </c>
@@ -9413,7 +9415,7 @@
         <v>9.4600000000000001E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>28.991340000000001</v>
       </c>
@@ -9472,7 +9474,7 @@
         <v>1.48E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>29.00169</v>
       </c>
@@ -9531,7 +9533,7 @@
         <v>2.3E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>29.039709999999999</v>
       </c>
@@ -9590,7 +9592,7 @@
         <v>8.6700000000000006E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>31.018160000000002</v>
       </c>
@@ -9649,7 +9651,7 @@
         <v>1.64E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>37.00564</v>
       </c>
@@ -9708,7 +9710,7 @@
         <v>4.7899999999999999E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
         <v>38.016129999999997</v>
       </c>
@@ -9767,7 +9769,7 @@
         <v>1.47E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>41.040759999999999</v>
       </c>
@@ -9826,7 +9828,7 @@
         <v>1.6899999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>42.011450000000004</v>
       </c>
@@ -9885,7 +9887,7 @@
         <v>5.8699999999999996E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>42.047199999999997</v>
       </c>
@@ -9944,7 +9946,7 @@
         <v>9.8700000000000003E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>43.018000000000001</v>
       </c>
@@ -10003,7 +10005,7 @@
         <v>7.7099999999999998E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>43.054760000000002</v>
       </c>
@@ -10062,7 +10064,7 @@
         <v>7.92E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
         <v>43.981389999999998</v>
       </c>
@@ -10121,7 +10123,7 @@
         <v>1.2199999999999999E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
         <v>44.022300000000001</v>
       </c>
@@ -10180,7 +10182,7 @@
         <v>2.1699999999999999E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
         <v>44.989939999999997</v>
       </c>
@@ -10239,7 +10241,7 @@
         <v>3.46E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
         <v>44.992800000000003</v>
       </c>
@@ -10298,7 +10300,7 @@
         <v>1.9E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>45.034390000000002</v>
       </c>
@@ -10357,7 +10359,7 @@
         <v>6.2600000000000004E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
         <v>47.012039999999999</v>
       </c>
@@ -10416,7 +10418,7 @@
         <v>2.4499999999999999E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>50.013379999999998</v>
       </c>
@@ -10475,7 +10477,7 @@
         <v>2.7799999999999999E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
         <v>51.022179999999999</v>
       </c>
@@ -10534,7 +10536,7 @@
         <v>1.11E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>51.986519999999999</v>
       </c>
@@ -10593,7 +10595,7 @@
         <v>2.6200000000000003E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
         <v>52.029089999999997</v>
       </c>
@@ -10652,7 +10654,7 @@
         <v>3.1700000000000001E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
         <v>52.991280000000003</v>
       </c>
@@ -10711,7 +10713,7 @@
         <v>6.7599999999999995E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
         <v>53.000439999999998</v>
       </c>
@@ -10770,7 +10772,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
         <v>53.038249999999998</v>
       </c>
@@ -10829,7 +10831,7 @@
         <v>6.28E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
         <v>54.044400000000003</v>
       </c>
@@ -10888,7 +10890,7 @@
         <v>7.0200000000000004E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
         <v>55.018479999999997</v>
       </c>
@@ -10947,7 +10949,7 @@
         <v>4.3E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
         <v>55.054949999999998</v>
       </c>
@@ -11006,7 +11008,7 @@
         <v>5.3200000000000001E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
         <v>56.023400000000002</v>
       </c>
@@ -11065,7 +11067,7 @@
         <v>2.9799999999999998E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
         <v>56.06</v>
       </c>
@@ -11124,7 +11126,7 @@
         <v>3.4499999999999998E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
         <v>57.033589999999997</v>
       </c>
@@ -11183,7 +11185,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
         <v>57.070720000000001</v>
       </c>
@@ -11242,7 +11244,7 @@
         <v>2.5799999999999998E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
         <v>57.998600000000003</v>
       </c>
@@ -11301,7 +11303,7 @@
         <v>2.34E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
         <v>59.007170000000002</v>
       </c>
@@ -11360,7 +11362,7 @@
         <v>6.5300000000000004E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
         <v>59.049599999999998</v>
       </c>
@@ -11419,7 +11421,7 @@
         <v>1.1800000000000001E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
         <v>59.999949999999998</v>
       </c>
@@ -11478,7 +11480,7 @@
         <v>2.0799999999999999E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
         <v>60.984189999999998</v>
       </c>
@@ -11537,7 +11539,7 @@
         <v>4.4600000000000004E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
         <v>61.003549999999997</v>
       </c>
@@ -11596,7 +11598,7 @@
         <v>1.0300000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
         <v>63.021059999999999</v>
       </c>
@@ -11655,7 +11657,7 @@
         <v>4.9500000000000004E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
         <v>64.029229999999998</v>
       </c>
@@ -11714,7 +11716,7 @@
         <v>1.06E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
         <v>65.039299999999997</v>
       </c>
@@ -11773,7 +11775,7 @@
         <v>4.4099999999999999E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
         <v>66.008840000000006</v>
       </c>
@@ -11832,7 +11834,7 @@
         <v>3.6600000000000001E-4</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
         <v>66.045529999999999</v>
       </c>
@@ -11891,7 +11893,7 @@
         <v>7.3300000000000004E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
         <v>67.017269999999996</v>
       </c>
@@ -11950,7 +11952,7 @@
         <v>6.1899999999999998E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
         <v>67.054659999999998</v>
       </c>
@@ -12009,7 +12011,7 @@
         <v>1.16E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
         <v>68.025239999999997</v>
       </c>
@@ -12068,7 +12070,7 @@
         <v>5.9900000000000003E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
         <v>68.059070000000006</v>
       </c>
@@ -12127,7 +12129,7 @@
         <v>1.8100000000000001E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
         <v>68.992239999999995</v>
       </c>
@@ -12186,7 +12188,7 @@
         <v>2.0300000000000001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
         <v>69.034080000000003</v>
       </c>
@@ -12245,7 +12247,7 @@
         <v>9.5600000000000004E-4</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
         <v>69.071209999999994</v>
       </c>
@@ -12304,7 +12306,7 @@
         <v>8.8199999999999997E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
         <v>69.955529999999996</v>
       </c>
@@ -12363,7 +12365,7 @@
         <v>6.5499999999999998E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
         <v>70.039060000000006</v>
       </c>
@@ -12422,7 +12424,7 @@
         <v>1.27E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
         <v>70.075140000000005</v>
       </c>
@@ -12481,7 +12483,7 @@
         <v>1.4300000000000001E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A65" s="4">
         <v>70.964749999999995</v>
       </c>
@@ -12540,7 +12542,7 @@
         <v>4.95E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
         <v>71.011650000000003</v>
       </c>
@@ -12599,7 +12601,7 @@
         <v>4.6000000000000001E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
         <v>71.051850000000002</v>
       </c>
@@ -12658,7 +12660,7 @@
         <v>2.8200000000000002E-4</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
         <v>73.990359999999995</v>
       </c>
@@ -12717,7 +12719,7 @@
         <v>2.6200000000000003E-4</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
         <v>74.012069999999994</v>
       </c>
@@ -12776,7 +12778,7 @@
         <v>1.2700000000000001E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
         <v>74.012289999999993</v>
       </c>
@@ -12835,7 +12837,7 @@
         <v>1.32E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
         <v>75.021429999999995</v>
       </c>
@@ -12894,7 +12896,7 @@
         <v>5.7299999999999999E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
         <v>76.029439999999994</v>
       </c>
@@ -12953,7 +12955,7 @@
         <v>2.98E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
         <v>77.000159999999994</v>
       </c>
@@ -13012,7 +13014,7 @@
         <v>5.8900000000000003E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
         <v>77.038300000000007</v>
       </c>
@@ -13071,7 +13073,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
         <v>78.044809999999998</v>
       </c>
@@ -13130,7 +13132,7 @@
         <v>8.9499999999999996E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
         <v>78.996139999999997</v>
       </c>
@@ -13189,7 +13191,7 @@
         <v>2.6200000000000003E-4</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
         <v>79.01652</v>
       </c>
@@ -13248,7 +13250,7 @@
         <v>5.6400000000000005E-4</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
         <v>79.053719999999998</v>
       </c>
@@ -13307,7 +13309,7 @@
         <v>2.1199999999999999E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
         <v>80.058310000000006</v>
       </c>
@@ -13366,7 +13368,7 @@
         <v>2.7300000000000002E-4</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
         <v>81.034869999999998</v>
       </c>
@@ -13425,7 +13427,7 @@
         <v>7.4700000000000005E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
         <v>81.070620000000005</v>
       </c>
@@ -13484,7 +13486,7 @@
         <v>4.3399999999999998E-4</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
         <v>81.998760000000004</v>
       </c>
@@ -13543,7 +13545,7 @@
         <v>3.79E-4</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
         <v>82.041309999999996</v>
       </c>
@@ -13602,7 +13604,7 @@
         <v>1.27E-4</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
         <v>83.007810000000006</v>
       </c>
@@ -13661,7 +13663,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
         <v>83.009309999999999</v>
       </c>
@@ -13720,7 +13722,7 @@
         <v>8.4699999999999999E-4</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
         <v>83.031720000000007</v>
       </c>
@@ -13779,7 +13781,7 @@
         <v>5.5599999999999996E-4</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
         <v>83.088099999999997</v>
       </c>
@@ -13838,7 +13840,7 @@
         <v>2.0599999999999999E-4</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
         <v>84.983059999999995</v>
       </c>
@@ -13897,7 +13899,7 @@
         <v>3.68E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A89" s="4">
         <v>85.006249999999994</v>
       </c>
@@ -13956,7 +13958,7 @@
         <v>2.3599999999999999E-4</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
         <v>86.011759999999995</v>
       </c>
@@ -14015,7 +14017,7 @@
         <v>6.1799999999999995E-4</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A91" s="4">
         <v>86.011790000000005</v>
       </c>
@@ -14074,7 +14076,7 @@
         <v>5.9199999999999997E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
         <v>86.958250000000007</v>
       </c>
@@ -14133,7 +14135,7 @@
         <v>3.5300000000000002E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A93" s="4">
         <v>87.001189999999994</v>
       </c>
@@ -14192,7 +14194,7 @@
         <v>2.99E-4</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
         <v>87.019970000000001</v>
       </c>
@@ -14251,7 +14253,7 @@
         <v>1.31E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
         <v>87.02037</v>
       </c>
@@ -14310,7 +14312,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
         <v>87.967209999999994</v>
       </c>
@@ -14369,7 +14371,7 @@
         <v>3.1799999999999998E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
         <v>88.026849999999996</v>
       </c>
@@ -14428,7 +14430,7 @@
         <v>4.6299999999999998E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
         <v>88.977819999999994</v>
       </c>
@@ -14487,7 +14489,7 @@
         <v>5.9900000000000003E-4</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A99" s="4">
         <v>89.036829999999995</v>
       </c>
@@ -14546,7 +14548,7 @@
         <v>1.91E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
         <v>90.044820000000001</v>
       </c>
@@ -14605,7 +14607,7 @@
         <v>1.67E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A101" s="4">
         <v>91.053790000000006</v>
       </c>
@@ -14664,7 +14666,7 @@
         <v>4.9500000000000004E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
         <v>92.025220000000004</v>
       </c>
@@ -14723,7 +14725,7 @@
         <v>3.9300000000000001E-4</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A103" s="4">
         <v>92.058499999999995</v>
       </c>
@@ -14782,7 +14784,7 @@
         <v>5.9000000000000003E-4</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
         <v>92.989369999999994</v>
       </c>
@@ -14841,7 +14843,7 @@
         <v>4.0099999999999999E-4</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
         <v>93.033550000000005</v>
       </c>
@@ -14900,7 +14902,7 @@
         <v>2.8899999999999998E-4</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
         <v>93.070139999999995</v>
       </c>
@@ -14959,7 +14961,7 @@
         <v>2.72E-4</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
         <v>94.039990000000003</v>
       </c>
@@ -15018,7 +15020,7 @@
         <v>2.0100000000000001E-4</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
         <v>94.962329999999994</v>
       </c>
@@ -15077,7 +15079,7 @@
         <v>5.1500000000000005E-4</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A109" s="4">
         <v>95.009</v>
       </c>
@@ -15136,7 +15138,7 @@
         <v>2.9500000000000001E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
         <v>95.010400000000004</v>
       </c>
@@ -15195,7 +15197,7 @@
         <v>3.5300000000000002E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A111" s="4">
         <v>95.049390000000002</v>
       </c>
@@ -15254,7 +15256,7 @@
         <v>2.9500000000000001E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
         <v>95.087019999999995</v>
       </c>
@@ -15313,7 +15315,7 @@
         <v>1.4100000000000001E-4</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A113" s="4">
         <v>98.011099999999999</v>
       </c>
@@ -15372,7 +15374,7 @@
         <v>4.37E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
         <v>98.011219999999994</v>
       </c>
@@ -15431,7 +15433,7 @@
         <v>3.8200000000000002E-4</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A115" s="4">
         <v>98.011430000000004</v>
       </c>
@@ -15490,7 +15492,7 @@
         <v>4.2299999999999998E-4</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
         <v>99.001429999999999</v>
       </c>
@@ -15549,7 +15551,7 @@
         <v>4.8799999999999999E-4</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
         <v>99.016869999999997</v>
       </c>
@@ -15608,7 +15610,7 @@
         <v>7.6800000000000002E-4</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A118" s="9">
         <v>99.020529999999994</v>
       </c>
